--- a/construction_quote_forms/017_wire_rods_price_quote_request_form--construction_quote_forms.xlsx
+++ b/construction_quote_forms/017_wire_rods_price_quote_request_form--construction_quote_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rod'}</t>
+          <t>rod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rod'}</t>
+          <t>Rod</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sheet'}</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sheet'}</t>
+          <t>Sheet</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'coil'}</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Coil'}</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1/2_inch'}</t>
+          <t>1/2_inch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1/2 inch'}</t>
+          <t>1/2 inch</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1/4_inch'}</t>
+          <t>1/4_inch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1/4 inch'}</t>
+          <t>1/4 inch</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'1/8_inch'}</t>
+          <t>1/8_inch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '1/8 inch'}</t>
+          <t>1/8 inch</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'3/8_inch'}</t>
+          <t>3/8_inch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '3/8 inch'}</t>
+          <t>3/8 inch</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'1/4_inch'}</t>
+          <t>3/16_inch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '1/4 inch'}</t>
+          <t>3/16 inch</t>
         </is>
       </c>
     </row>
@@ -1267,46 +1267,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'3/16_inch'}</t>
+          <t>5/8_inch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '3/16 inch'}</t>
+          <t>5/8 inch</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>product_width_choices</t>
+          <t>product_length_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'1/2_inch'}</t>
+          <t>10_ft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': '1/2 inch'}</t>
+          <t>10 ft</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>product_width_choices</t>
+          <t>product_length_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'5/8_inch'}</t>
+          <t>25_ft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': '5/8 inch'}</t>
+          <t>25 ft</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'10_ft'}</t>
+          <t>50_ft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '10 ft'}</t>
+          <t>50 ft</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'25_ft'}</t>
+          <t>100_ft</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '25 ft'}</t>
+          <t>100 ft</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'50_ft'}</t>
+          <t>150_ft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '50 ft'}</t>
+          <t>150 ft</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'100_ft'}</t>
+          <t>200_ft</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '100 ft'}</t>
+          <t>200 ft</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'150_ft'}</t>
+          <t>250_ft</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '150 ft'}</t>
+          <t>250 ft</t>
         </is>
       </c>
     </row>
@@ -1403,46 +1403,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'200_ft'}</t>
+          <t>500_ft</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '200 ft'}</t>
+          <t>500 ft</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>product_length_choices</t>
+          <t>material_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'250_ft'}</t>
+          <t>aluminum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': '250 ft'}</t>
+          <t>Aluminum</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>product_length_choices</t>
+          <t>material_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'500_ft'}</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': '500 ft'}</t>
+          <t>Steel</t>
         </is>
       </c>
     </row>
@@ -1454,46 +1454,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'aluminum'}</t>
+          <t>galvanized_steel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Aluminum'}</t>
+          <t>Galvanized Steel</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>material_choices</t>
+          <t>customer_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'steel'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Steel'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>material_choices</t>
+          <t>customer_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'galvanized_steel'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Galvanized Steel'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1505,46 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>customer_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'jane'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Jane'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>customer_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'joe'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Joe'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
